--- a/Questions - Round 2.xlsx
+++ b/Questions - Round 2.xlsx
@@ -1,14 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_1676B7FEC8096CD1BD465F955E707CF0E4F5FC6D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9EBB330-21E5-4640-8F90-410EC007755D}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innochemnv-my.sharepoint.com/personal/zander_fias_innochem_be/Documents/OneDrive_1_25-9-2026/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="93" documentId="11_1676B7FEC8096CD1BD465F955E707CF0E4F5FC6D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1E2CDD7-A00D-4C2A-B30E-2A37131B6193}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="28770" windowHeight="15570" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EN" sheetId="1" r:id="rId1"/>
+    <sheet name="NL" sheetId="2" r:id="rId2"/>
+    <sheet name="FR" sheetId="3" r:id="rId3"/>
+    <sheet name="GE" sheetId="4" r:id="rId4"/>
+    <sheet name="SP" sheetId="5" r:id="rId5"/>
+    <sheet name="IT" sheetId="6" r:id="rId6"/>
+    <sheet name="PL" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -31,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="428">
   <si>
     <t>type</t>
   </si>
@@ -253,13 +264,1075 @@
   </si>
   <si>
     <t>Accessible explanations make learning inclusive and useful. Personal habits matter because many small choices become meaningful when repeated by many people.</t>
+  </si>
+  <si>
+    <t>Wat is de kerngedachte achter SDG 4 – Kwaliteitsonderwijs?</t>
+  </si>
+  <si>
+    <t>Makkelijk · Eén antwoord</t>
+  </si>
+  <si>
+    <t>Het is alleen van toepassing op nationale overheden.</t>
+  </si>
+  <si>
+    <t>Het richt zich op een leven lang leren.</t>
+  </si>
+  <si>
+    <t>Het vraagt bedrijven om langetermijneffecten te negeren.</t>
+  </si>
+  <si>
+    <t>Het is alleen een marketingslogan zonder praktische betekenis.</t>
+  </si>
+  <si>
+    <t>SDG 4 gaat over een leven lang leren en het omzetten van die doelstelling in praktische actie. SDG 4 wordt nuttig wanneer mensen het brede doel vertalen naar praktische beslissingen.</t>
+  </si>
+  <si>
+    <t>Waarom is SDG 4 relevant voor een bedrijf dat chemicaliën distribueert en produceert?</t>
+  </si>
+  <si>
+    <t>Gemiddeld · Eén antwoord</t>
+  </si>
+  <si>
+    <t>Omdat chemicaliën niets met duurzaamheid te maken hebben.</t>
+  </si>
+  <si>
+    <t>Omdat duurzaamheid alleen in jaarverslagen thuishoort.</t>
+  </si>
+  <si>
+    <t>Omdat opleiding, kennisdeling en veilig werken de duurzaamheidsprestaties kunnen beïnvloeden.</t>
+  </si>
+  <si>
+    <t>Omdat de SDG's alle wettelijke vereisten vervangen.</t>
+  </si>
+  <si>
+    <t>Opleiding, kennisdeling en veilig werken zijn praktische gebieden waarop een bedrijf een verschil kan maken. De SDG's verbinden mondiale doelen met dagelijkse operationele keuzes.</t>
+  </si>
+  <si>
+    <t>Welke uitspraak is een veelvoorkomende misvatting over SDG 4?</t>
+  </si>
+  <si>
+    <t>SDG 4 kan aan dagelijkse beslissingen worden gekoppeld.</t>
+  </si>
+  <si>
+    <t>Bedrijven kunnen relevante effecten meten en verbeteren.</t>
+  </si>
+  <si>
+    <t>Medewerkers kunnen met kleine gewoonten bijdragen.</t>
+  </si>
+  <si>
+    <t>Onderwijs stopt na school.</t>
+  </si>
+  <si>
+    <t>Dit is de misvatting: ze maakt de SDG te beperkt en verbergt praktische kansen. Een goede quizvraag stelt vaak een misvatting ter discussie, omdat de leerstof daardoor beter blijft hangen.</t>
+  </si>
+  <si>
+    <t>Welk gedrag zet SDG 4 het best om van theorie naar actie?</t>
+  </si>
+  <si>
+    <t>Een concrete verbetering kiezen en die ook uitvoeren.</t>
+  </si>
+  <si>
+    <t>Het tegenovergestelde doen wanneer niemand controleert.</t>
+  </si>
+  <si>
+    <t>Wachten tot iemand anders alles oplost.</t>
+  </si>
+  <si>
+    <t>Over duurzaamheid praten maar niets veranderen.</t>
+  </si>
+  <si>
+    <t>Concrete actie zorgt voor leren en meetbare verbetering. Bewustzijn rond duurzaamheid moet leiden tot praktische gedragsverandering.</t>
+  </si>
+  <si>
+    <t>Wat maakt SDG 4 een nuttig leeronderwerp voor medewerkers?</t>
+  </si>
+  <si>
+    <t>Het geeft voor elke situatie één perfect antwoord.</t>
+  </si>
+  <si>
+    <t>Het verbindt mondiale uitdagingen met keuzes die mensen op het werk en thuis herkennen.</t>
+  </si>
+  <si>
+    <t>Het heeft niets met de bedrijfscultuur te maken.</t>
+  </si>
+  <si>
+    <t>Het maakt vakkennis overbodig.</t>
+  </si>
+  <si>
+    <t>Het sterkste leereffect ontstaat wanneer mensen het verband zien tussen mondiale doelen en vertrouwde keuzes. De SDG's zijn het boeiendst wanneer ze relevant, concreet en verbonden met de rollen van mensen aanvoelen.</t>
+  </si>
+  <si>
+    <t>Wat is het hoofddoel van het YouPro-programma?</t>
+  </si>
+  <si>
+    <t>Een programma uitsluitend voor externe leveranciers</t>
+  </si>
+  <si>
+    <t>Alleen kortlopende verkoopacties</t>
+  </si>
+  <si>
+    <t>Persoonlijke ontwikkeling en internationale netwerking van jonge professionals</t>
+  </si>
+  <si>
+    <t>Een vervanging voor alle technische opleidingen</t>
+  </si>
+  <si>
+    <t>Het verslag beschrijft YouPro als een programma van 24 maanden voor persoonlijke ontwikkeling en internationale netwerking. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij mondiale doelen.</t>
+  </si>
+  <si>
+    <t>Welk YouPro-project vergroot het bewustzijn rond verantwoord gebruik van kantoorhulpmiddelen?</t>
+  </si>
+  <si>
+    <t>Moeilijk · Eén antwoord</t>
+  </si>
+  <si>
+    <t>PaperSaver wordt beschreven als een project dat het bewustzijn rond verantwoord gebruik van hulpmiddelen in het dagelijkse kantoorleven vergroot. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij mondiale doelen.</t>
+  </si>
+  <si>
+    <t>Hoe ondersteunt het Sustainability Ambassador Team leren?</t>
+  </si>
+  <si>
+    <t>Door ideeën uit te wisselen en gezamenlijke duurzaamheidsinitiatieven te ontwikkelen</t>
+  </si>
+  <si>
+    <t>Door contact tussen landen te vermijden</t>
+  </si>
+  <si>
+    <t>Door duurzaamheid tot één locatie te beperken</t>
+  </si>
+  <si>
+    <t>Door alle verantwoordelijkheden van medewerkers over te nemen</t>
+  </si>
+  <si>
+    <t>Het verslag legt uit dat ambassadeurs samenkomen om ideeën uit te wisselen en duurzaamheidsinitiatieven verder te ontwikkelen. Voorbeelden van STOCKMEIER maken de SDG concreet en tonen hoe initiatieven van de Groep aansluiten bij mondiale doelen.</t>
+  </si>
+  <si>
+    <t>Welke actie in het privéleven ondersteunt SDG 4 het best?</t>
+  </si>
+  <si>
+    <t>Desinformatie snel delen</t>
+  </si>
+  <si>
+    <t>Leren hoe dagelijkse keuzes duurzaamheid beïnvloeden</t>
+  </si>
+  <si>
+    <t>Aannemen dat leren alleen voor studenten is</t>
+  </si>
+  <si>
+    <t>Nieuwe informatie vermijden</t>
+  </si>
+  <si>
+    <t>Leren helpt mensen ook buiten het werk betere beslissingen te nemen. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Wat is een praktische manier om anderen te helpen leren?</t>
+  </si>
+  <si>
+    <t>Nuttige kennis geheimhouden</t>
+  </si>
+  <si>
+    <t>Mensen uitlachen die vragen stellen</t>
+  </si>
+  <si>
+    <t>Een nuttige duurzaamheidsgewoonte in eenvoudige taal uitleggen</t>
+  </si>
+  <si>
+    <t>Alleen in ingewikkelde technische termen spreken</t>
+  </si>
+  <si>
+    <t>Toegankelijke uitleg maakt leren inclusief en nuttig. Persoonlijke gewoonten zijn belangrijk omdat veel kleine keuzes betekenisvol worden wanneer veel mensen ze herhalen.</t>
+  </si>
+  <si>
+    <t>Quelle est l’idée principale de l’ODD 4 – Éducation de qualité ?</t>
+  </si>
+  <si>
+    <t>Facile · Choix unique</t>
+  </si>
+  <si>
+    <t>Il s’applique uniquement aux gouvernements nationaux.</t>
+  </si>
+  <si>
+    <t>Il met l’accent sur l’apprentissage tout au long de la vie.</t>
+  </si>
+  <si>
+    <t>Il demande aux entreprises d’ignorer les impacts à long terme.</t>
+  </si>
+  <si>
+    <t>Ce n’est qu’un slogan marketing sans signification pratique.</t>
+  </si>
+  <si>
+    <t>L’ODD 4 concerne l’apprentissage tout au long de la vie et la transformation de cet objectif en actions concrètes. L’ODD 4 devient utile lorsque les personnes traduisent cet objectif général en décisions pratiques.</t>
+  </si>
+  <si>
+    <t>Pourquoi l’ODD 4 est-il pertinent pour une entreprise de distribution et de production de produits chimiques ?</t>
+  </si>
+  <si>
+    <t>Moyen · Choix unique</t>
+  </si>
+  <si>
+    <t>Parce que les produits chimiques n’ont aucun lien avec la durabilité.</t>
+  </si>
+  <si>
+    <t>Parce que la durabilité n’a sa place que dans les rapports annuels.</t>
+  </si>
+  <si>
+    <t>Parce que la formation, le partage des connaissances et la sécurité au travail peuvent influencer les performances en matière de durabilité.</t>
+  </si>
+  <si>
+    <t>Parce que les ODD remplacent toutes les exigences légales.</t>
+  </si>
+  <si>
+    <t>La formation, le partage des connaissances et la sécurité au travail sont des domaines concrets dans lesquels une entreprise peut faire la différence. Les ODD relient les objectifs mondiaux aux choix opérationnels quotidiens.</t>
+  </si>
+  <si>
+    <t>Quelle affirmation constitue une idée fausse courante sur l’ODD 4 ?</t>
+  </si>
+  <si>
+    <t>L’ODD 4 peut être lié aux décisions quotidiennes.</t>
+  </si>
+  <si>
+    <t>Les entreprises peuvent mesurer et améliorer les impacts pertinents.</t>
+  </si>
+  <si>
+    <t>Les collaborateurs peuvent contribuer par de petites habitudes.</t>
+  </si>
+  <si>
+    <t>L’éducation s’arrête après l’école.</t>
+  </si>
+  <si>
+    <t>C’est l’idée fausse : elle réduit excessivement la portée de l’ODD et masque des possibilités concrètes. Une bonne question de quiz remet souvent en cause une idée fausse, car cela rend l’apprentissage plus mémorable.</t>
+  </si>
+  <si>
+    <t>Quel comportement transforme le mieux l’ODD 4 de la théorie en action ?</t>
+  </si>
+  <si>
+    <t>Choisir une amélioration concrète et la mettre en œuvre.</t>
+  </si>
+  <si>
+    <t>Faire le contraire lorsque personne ne vérifie.</t>
+  </si>
+  <si>
+    <t>Attendre que quelqu’un d’autre règle tout.</t>
+  </si>
+  <si>
+    <t>Parler de durabilité sans rien changer.</t>
+  </si>
+  <si>
+    <t>Une action concrète crée de l’apprentissage et une amélioration mesurable. La sensibilisation à la durabilité doit conduire à un changement de comportement concret.</t>
+  </si>
+  <si>
+    <t>Pourquoi l’ODD 4 est-il un sujet d’apprentissage utile pour les collaborateurs ?</t>
+  </si>
+  <si>
+    <t>Il donne une réponse parfaite à chaque situation.</t>
+  </si>
+  <si>
+    <t>Il relie les défis mondiaux à des choix que les personnes reconnaissent au travail et à la maison.</t>
+  </si>
+  <si>
+    <t>Il n’a aucun rapport avec la culture d’entreprise.</t>
+  </si>
+  <si>
+    <t>Il supprime le besoin de connaissances spécialisées.</t>
+  </si>
+  <si>
+    <t>L’apprentissage est le plus efficace lorsque les personnes voient le lien entre les objectifs mondiaux et des choix familiers. Les ODD sont les plus engageants lorsqu’ils paraissent pertinents, concrets et liés aux rôles de chacun.</t>
+  </si>
+  <si>
+    <t>Que vise principalement à renforcer le programme YouPro ?</t>
+  </si>
+  <si>
+    <t>Un programme réservé aux fournisseurs externes</t>
+  </si>
+  <si>
+    <t>Uniquement des promotions commerciales à court terme</t>
+  </si>
+  <si>
+    <t>Le développement personnel et le réseautage international des jeunes professionnels</t>
+  </si>
+  <si>
+    <t>Le remplacement de toutes les formations techniques</t>
+  </si>
+  <si>
+    <t>Le rapport décrit YouPro comme un programme de 24 mois consacré au développement personnel et au réseautage international. Les exemples de STOCKMEIER rendent l’ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Quel projet YouPro sensibilise à une utilisation responsable des ressources de bureau ?</t>
+  </si>
+  <si>
+    <t>Difficile · Choix unique</t>
+  </si>
+  <si>
+    <t>PaperSaver est décrit comme un projet de sensibilisation à l’utilisation responsable des ressources dans la vie quotidienne au bureau. Les exemples de STOCKMEIER rendent l’ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Comment l’équipe des ambassadeurs du développement durable soutient-elle l’apprentissage ?</t>
+  </si>
+  <si>
+    <t>En échangeant des idées et en développant des initiatives communes de durabilité</t>
+  </si>
+  <si>
+    <t>En évitant les contacts entre pays</t>
+  </si>
+  <si>
+    <t>En limitant la durabilité à un seul site</t>
+  </si>
+  <si>
+    <t>En remplaçant toutes les responsabilités des collaborateurs</t>
+  </si>
+  <si>
+    <t>Le rapport explique que les ambassadeurs se réunissent pour échanger des idées et développer davantage les initiatives de durabilité. Les exemples de STOCKMEIER rendent l’ODD concret et montrent comment les initiatives du Groupe sont liées aux objectifs mondiaux.</t>
+  </si>
+  <si>
+    <t>Dans la vie privée, quelle action soutient le mieux l’ODD 4 ?</t>
+  </si>
+  <si>
+    <t>Partager rapidement de fausses informations</t>
+  </si>
+  <si>
+    <t>Apprendre comment les choix quotidiens influencent la durabilité</t>
+  </si>
+  <si>
+    <t>Supposer que l’apprentissage est réservé aux étudiants</t>
+  </si>
+  <si>
+    <t>Éviter les nouvelles informations</t>
+  </si>
+  <si>
+    <t>L’apprentissage aide aussi les personnes à prendre de meilleures décisions en dehors du travail. Les habitudes personnelles comptent, car de nombreux petits choix deviennent significatifs lorsqu’ils sont répétés par beaucoup de personnes.</t>
+  </si>
+  <si>
+    <t>Quelle est une manière concrète d’aider les autres à apprendre ?</t>
+  </si>
+  <si>
+    <t>Garder les connaissances utiles secrètes</t>
+  </si>
+  <si>
+    <t>Se moquer des personnes qui posent des questions</t>
+  </si>
+  <si>
+    <t>Expliquer une habitude utile en matière de durabilité dans un langage simple</t>
+  </si>
+  <si>
+    <t>Parler uniquement avec des termes techniques compliqués</t>
+  </si>
+  <si>
+    <t>Des explications accessibles rendent l’apprentissage inclusif et utile. Les habitudes personnelles comptent, car de nombreux petits choix deviennent significatifs lorsqu’ils sont répétés par beaucoup de personnes.</t>
+  </si>
+  <si>
+    <t>Was ist der Kerngedanke von SDG 4 – Hochwertige Bildung?</t>
+  </si>
+  <si>
+    <t>Leicht · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Es gilt nur für nationale Regierungen.</t>
+  </si>
+  <si>
+    <t>Es konzentriert sich auf lebenslanges Lernen.</t>
+  </si>
+  <si>
+    <t>Es fordert Unternehmen auf, langfristige Auswirkungen zu ignorieren.</t>
+  </si>
+  <si>
+    <t>Es ist nur ein Marketingslogan ohne praktische Bedeutung.</t>
+  </si>
+  <si>
+    <t>Bei SDG 4 geht es um lebenslanges Lernen und darum, dieses Ziel in konkrete Maßnahmen umzusetzen. SDG 4 wird nützlich, wenn Menschen das übergeordnete Ziel in praktische Entscheidungen übersetzen.</t>
+  </si>
+  <si>
+    <t>Warum ist SDG 4 für ein Unternehmen relevant, das Chemikalien vertreibt und produziert?</t>
+  </si>
+  <si>
+    <t>Mittel · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>Weil Chemikalien keinen Bezug zur Nachhaltigkeit haben.</t>
+  </si>
+  <si>
+    <t>Weil Nachhaltigkeit nur in Geschäftsberichte gehört.</t>
+  </si>
+  <si>
+    <t>Weil Schulungen, Wissensaustausch und sicheres Arbeiten die Nachhaltigkeitsleistung beeinflussen können.</t>
+  </si>
+  <si>
+    <t>Weil die SDGs alle gesetzlichen Anforderungen ersetzen.</t>
+  </si>
+  <si>
+    <t>Schulungen, Wissensaustausch und sicheres Arbeiten sind praktische Bereiche, in denen ein Unternehmen etwas bewirken kann. Die SDGs verbinden globale Ziele mit täglichen betrieblichen Entscheidungen.</t>
+  </si>
+  <si>
+    <t>Welche Aussage ist ein häufiges Missverständnis über SDG 4?</t>
+  </si>
+  <si>
+    <t>SDG 4 kann mit täglichen Entscheidungen verknüpft werden.</t>
+  </si>
+  <si>
+    <t>Unternehmen können relevante Auswirkungen messen und verbessern.</t>
+  </si>
+  <si>
+    <t>Mitarbeitende können durch kleine Gewohnheiten beitragen.</t>
+  </si>
+  <si>
+    <t>Bildung endet nach der Schule.</t>
+  </si>
+  <si>
+    <t>Das ist das Missverständnis: Es fasst das SDG zu eng und verdeckt praktische Möglichkeiten. Eine gute Quizfrage hinterfragt oft ein Missverständnis, weil dadurch das Gelernte besser im Gedächtnis bleibt.</t>
+  </si>
+  <si>
+    <t>Welches Verhalten setzt SDG 4 am besten von der Theorie in die Praxis um?</t>
+  </si>
+  <si>
+    <t>Eine konkrete Verbesserung auswählen und konsequent umsetzen.</t>
+  </si>
+  <si>
+    <t>Das Gegenteil tun, wenn niemand kontrolliert.</t>
+  </si>
+  <si>
+    <t>Warten, bis jemand anderes alles löst.</t>
+  </si>
+  <si>
+    <t>Über Nachhaltigkeit sprechen, aber nichts verändern.</t>
+  </si>
+  <si>
+    <t>Konkretes Handeln schafft Lernerfahrungen und messbare Verbesserungen. Nachhaltigkeitsbewusstsein sollte zu praktischen Verhaltensänderungen führen.</t>
+  </si>
+  <si>
+    <t>Was macht SDG 4 zu einem nützlichen Lernthema für Mitarbeitende?</t>
+  </si>
+  <si>
+    <t>Es liefert eine perfekte Antwort für jede Situation.</t>
+  </si>
+  <si>
+    <t>Es verbindet globale Herausforderungen mit Entscheidungen, die Menschen bei der Arbeit und zu Hause wiedererkennen.</t>
+  </si>
+  <si>
+    <t>Es hat keinen Bezug zur Unternehmenskultur.</t>
+  </si>
+  <si>
+    <t>Es macht Fachwissen überflüssig.</t>
+  </si>
+  <si>
+    <t>Der größte Lernerfolg entsteht, wenn Menschen die Verbindung zwischen globalen Zielen und vertrauten Entscheidungen erkennen. Die SDGs sind besonders motivierend, wenn sie relevant, konkret und mit den Rollen der Menschen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Was soll das YouPro-Programm hauptsächlich stärken?</t>
+  </si>
+  <si>
+    <t>Ein Programm nur für externe Lieferanten</t>
+  </si>
+  <si>
+    <t>Nur kurzfristige Verkaufsaktionen</t>
+  </si>
+  <si>
+    <t>Die persönliche Entwicklung und internationale Vernetzung junger Fachkräfte</t>
+  </si>
+  <si>
+    <t>Einen Ersatz für alle technischen Schulungen</t>
+  </si>
+  <si>
+    <t>Der Bericht beschreibt YouPro als ein 24-monatiges Programm zur persönlichen Entwicklung und internationalen Vernetzung. Die STOCKMEIER-Beispiele machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welches YouPro-Projekt sensibilisiert für einen verantwortungsvollen Umgang mit Büroressourcen?</t>
+  </si>
+  <si>
+    <t>Schwer · Einfachauswahl</t>
+  </si>
+  <si>
+    <t>PaperSaver wird als Projekt beschrieben, das für einen verantwortungsvollen Ressourceneinsatz im Büroalltag sensibilisiert. Die STOCKMEIER-Beispiele machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Wie unterstützt das Sustainability Ambassador Team das Lernen?</t>
+  </si>
+  <si>
+    <t>Durch den Austausch von Ideen und die Entwicklung gemeinsamer Nachhaltigkeitsinitiativen</t>
+  </si>
+  <si>
+    <t>Durch die Vermeidung länderübergreifender Kontakte</t>
+  </si>
+  <si>
+    <t>Durch die Beschränkung von Nachhaltigkeit auf einen Standort</t>
+  </si>
+  <si>
+    <t>Durch die Übernahme aller Verantwortlichkeiten der Mitarbeitenden</t>
+  </si>
+  <si>
+    <t>Der Bericht erklärt, dass sich die Botschafter treffen, um Ideen auszutauschen und Nachhaltigkeitsinitiativen weiterzuentwickeln. Die STOCKMEIER-Beispiele machen das SDG konkret und zeigen, wie Initiativen der Gruppe mit globalen Zielen verbunden sind.</t>
+  </si>
+  <si>
+    <t>Welche Handlung unterstützt SDG 4 im Privatleben am besten?</t>
+  </si>
+  <si>
+    <t>Falschinformationen schnell weitergeben</t>
+  </si>
+  <si>
+    <t>Lernen, wie tägliche Entscheidungen die Nachhaltigkeit beeinflussen</t>
+  </si>
+  <si>
+    <t>Annehmen, dass Lernen nur für Studierende bestimmt ist</t>
+  </si>
+  <si>
+    <t>Neue Informationen vermeiden</t>
+  </si>
+  <si>
+    <t>Lernen hilft Menschen auch außerhalb der Arbeit, bessere Entscheidungen zu treffen. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
+    <t>Wie kann man anderen auf praktische Weise beim Lernen helfen?</t>
+  </si>
+  <si>
+    <t>Nützliches Wissen geheim halten</t>
+  </si>
+  <si>
+    <t>Menschen verspotten, die Fragen stellen</t>
+  </si>
+  <si>
+    <t>Eine nützliche Nachhaltigkeitsgewohnheit in einfacher Sprache erklären</t>
+  </si>
+  <si>
+    <t>Nur in komplizierten Fachbegriffen sprechen</t>
+  </si>
+  <si>
+    <t>Verständliche Erklärungen machen Lernen inklusiv und nützlich. Persönliche Gewohnheiten sind wichtig, weil viele kleine Entscheidungen bedeutsam werden, wenn sie von vielen Menschen wiederholt werden.</t>
+  </si>
+  <si>
+    <t>¿Cuál es la idea principal del ODS 4 – Educación de calidad?</t>
+  </si>
+  <si>
+    <t>Fácil · Opción única</t>
+  </si>
+  <si>
+    <t>Solo se aplica a los gobiernos nacionales.</t>
+  </si>
+  <si>
+    <t>Se centra en el aprendizaje permanente.</t>
+  </si>
+  <si>
+    <t>Pide a las empresas que ignoren los impactos a largo plazo.</t>
+  </si>
+  <si>
+    <t>Es solo un eslogan de marketing sin significado práctico.</t>
+  </si>
+  <si>
+    <t>El ODS 4 trata del aprendizaje permanente y de convertir ese objetivo en acciones prácticas. El ODS 4 resulta útil cuando las personas traducen el objetivo general en decisiones concretas.</t>
+  </si>
+  <si>
+    <t>¿Por qué es relevante el ODS 4 para una empresa de distribución y producción de productos químicos?</t>
+  </si>
+  <si>
+    <t>Media · Opción única</t>
+  </si>
+  <si>
+    <t>Porque los productos químicos no tienen relación con la sostenibilidad.</t>
+  </si>
+  <si>
+    <t>Porque la sostenibilidad solo debe aparecer en los informes anuales.</t>
+  </si>
+  <si>
+    <t>Porque la formación, el intercambio de conocimientos y el trabajo seguro pueden influir en el desempeño en sostenibilidad.</t>
+  </si>
+  <si>
+    <t>Porque los ODS sustituyen todos los requisitos legales.</t>
+  </si>
+  <si>
+    <t>La formación, el intercambio de conocimientos y el trabajo seguro son ámbitos prácticos en los que una empresa puede marcar la diferencia. Los ODS conectan los objetivos globales con las decisiones operativas diarias.</t>
+  </si>
+  <si>
+    <t>¿Qué afirmación es un malentendido habitual sobre el ODS 4?</t>
+  </si>
+  <si>
+    <t>El ODS 4 puede vincularse a las decisiones diarias.</t>
+  </si>
+  <si>
+    <t>Las empresas pueden medir y mejorar los impactos relevantes.</t>
+  </si>
+  <si>
+    <t>Los empleados pueden contribuir mediante pequeños hábitos.</t>
+  </si>
+  <si>
+    <t>La educación termina después de la escuela.</t>
+  </si>
+  <si>
+    <t>Este es el malentendido: limita demasiado el ODS y oculta oportunidades prácticas. Una buena pregunta de cuestionario suele cuestionar un malentendido, porque así el aprendizaje se recuerda mejor.</t>
+  </si>
+  <si>
+    <t>¿Qué comportamiento convierte mejor el ODS 4 de la teoría en acción?</t>
+  </si>
+  <si>
+    <t>Elegir una mejora concreta y llevarla a cabo.</t>
+  </si>
+  <si>
+    <t>Hacer lo contrario cuando nadie está comprobando.</t>
+  </si>
+  <si>
+    <t>Esperar a que otra persona lo solucione todo.</t>
+  </si>
+  <si>
+    <t>Hablar de sostenibilidad sin cambiar nada.</t>
+  </si>
+  <si>
+    <t>La acción concreta genera aprendizaje y mejoras medibles. La conciencia sobre sostenibilidad debe conducir a un cambio de comportamiento práctico.</t>
+  </si>
+  <si>
+    <t>¿Qué hace que el ODS 4 sea un tema de aprendizaje útil para los empleados?</t>
+  </si>
+  <si>
+    <t>Ofrece una respuesta perfecta para cada situación.</t>
+  </si>
+  <si>
+    <t>Relaciona los retos globales con decisiones que las personas reconocen en el trabajo y en casa.</t>
+  </si>
+  <si>
+    <t>No tiene relación con la cultura empresarial.</t>
+  </si>
+  <si>
+    <t>Elimina la necesidad de conocimientos especializados.</t>
+  </si>
+  <si>
+    <t>El aprendizaje más sólido se produce cuando las personas ven la conexión entre los objetivos globales y las decisiones cotidianas. Los ODS resultan más atractivos cuando parecen relevantes, concretos y vinculados a las funciones de las personas.</t>
+  </si>
+  <si>
+    <t>¿Qué pretende reforzar principalmente el programa YouPro?</t>
+  </si>
+  <si>
+    <t>Un programa solo para proveedores externos</t>
+  </si>
+  <si>
+    <t>Únicamente promociones de ventas a corto plazo</t>
+  </si>
+  <si>
+    <t>El desarrollo personal y la creación de redes internacionales de jóvenes profesionales</t>
+  </si>
+  <si>
+    <t>Un sustituto de toda la formación técnica</t>
+  </si>
+  <si>
+    <t>El informe describe YouPro como un programa de 24 meses para el desarrollo personal y la creación de redes internacionales. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>¿Qué proyecto de YouPro conciencia sobre el uso responsable de los recursos de oficina?</t>
+  </si>
+  <si>
+    <t>Difícil · Opción única</t>
+  </si>
+  <si>
+    <t>PaperSaver se describe como un proyecto que conciencia sobre el uso responsable de los recursos en la vida diaria de la oficina. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>¿Cómo apoya el equipo de embajadores de sostenibilidad el aprendizaje?</t>
+  </si>
+  <si>
+    <t>Intercambiando ideas y desarrollando iniciativas conjuntas de sostenibilidad</t>
+  </si>
+  <si>
+    <t>Evitando el contacto entre países</t>
+  </si>
+  <si>
+    <t>Limitando la sostenibilidad a una sola ubicación</t>
+  </si>
+  <si>
+    <t>Sustituyendo todas las responsabilidades de los empleados</t>
+  </si>
+  <si>
+    <t>El informe explica que los embajadores se reúnen para intercambiar ideas y seguir desarrollando iniciativas de sostenibilidad. Los ejemplos de STOCKMEIER hacen concreto el ODS y muestran cómo las iniciativas del Grupo se conectan con los objetivos globales.</t>
+  </si>
+  <si>
+    <t>En la vida privada, ¿qué acción apoya mejor el ODS 4?</t>
+  </si>
+  <si>
+    <t>Compartir rápidamente información falsa</t>
+  </si>
+  <si>
+    <t>Aprender cómo las decisiones diarias afectan a la sostenibilidad</t>
+  </si>
+  <si>
+    <t>Suponer que aprender es solo para estudiantes</t>
+  </si>
+  <si>
+    <t>Evitar información nueva</t>
+  </si>
+  <si>
+    <t>Aprender también ayuda a las personas a tomar mejores decisiones fuera del trabajo. Los hábitos personales importan porque muchas pequeñas decisiones se vuelven significativas cuando muchas personas las repiten.</t>
+  </si>
+  <si>
+    <t>¿Cuál es una forma práctica de ayudar a otras personas a aprender?</t>
+  </si>
+  <si>
+    <t>Mantener en secreto los conocimientos útiles</t>
+  </si>
+  <si>
+    <t>Burlarse de quienes hacen preguntas</t>
+  </si>
+  <si>
+    <t>Explicar un hábito útil de sostenibilidad con un lenguaje sencillo</t>
+  </si>
+  <si>
+    <t>Hablar solo con términos técnicos complicados</t>
+  </si>
+  <si>
+    <t>Las explicaciones accesibles hacen que el aprendizaje sea inclusivo y útil. Los hábitos personales importan porque muchas pequeñas decisiones se vuelven significativas cuando muchas personas las repiten.</t>
+  </si>
+  <si>
+    <t>Jaka jest główna idea Celu Zrównoważonego Rozwoju 4 – Dobra jakość edukacji?</t>
+  </si>
+  <si>
+    <t>Łatwe · Jednokrotny wybór</t>
+  </si>
+  <si>
+    <t>Dotyczy wyłącznie rządów krajowych.</t>
+  </si>
+  <si>
+    <t>Koncentruje się na uczeniu się przez całe życie.</t>
+  </si>
+  <si>
+    <t>Wymaga od firm ignorowania długoterminowych skutków.</t>
+  </si>
+  <si>
+    <t>Jest jedynie hasłem marketingowym bez praktycznego znaczenia.</t>
+  </si>
+  <si>
+    <t>Cel 4 dotyczy uczenia się przez całe życie i przekładania tego celu na praktyczne działania. Staje się użyteczny, gdy ludzie przekładają ogólny cel na konkretne decyzje.</t>
+  </si>
+  <si>
+    <t>Dlaczego Cel 4 jest istotny dla firmy zajmującej się dystrybucją i produkcją chemikaliów?</t>
+  </si>
+  <si>
+    <t>Średnie · Jednokrotny wybór</t>
+  </si>
+  <si>
+    <t>Ponieważ chemikalia nie mają związku ze zrównoważonym rozwojem.</t>
+  </si>
+  <si>
+    <t>Ponieważ zrównoważony rozwój powinien pojawiać się tylko w raportach rocznych.</t>
+  </si>
+  <si>
+    <t>Ponieważ szkolenia, dzielenie się wiedzą i bezpieczna praca mogą wpływać na wyniki w zakresie zrównoważonego rozwoju.</t>
+  </si>
+  <si>
+    <t>Ponieważ cele zrównoważonego rozwoju zastępują wszystkie wymogi prawne.</t>
+  </si>
+  <si>
+    <t>Szkolenia, dzielenie się wiedzą i bezpieczna praca to praktyczne obszary, w których firma może coś zmienić. Cele zrównoważonego rozwoju łączą globalne założenia z codziennymi decyzjami operacyjnymi.</t>
+  </si>
+  <si>
+    <t>Które stwierdzenie jest częstym nieporozumieniem dotyczącym Celu 4?</t>
+  </si>
+  <si>
+    <t>Cel 4 można powiązać z codziennymi decyzjami.</t>
+  </si>
+  <si>
+    <t>Firmy mogą mierzyć i poprawiać istotne oddziaływania.</t>
+  </si>
+  <si>
+    <t>Pracownicy mogą wnosić wkład poprzez drobne nawyki.</t>
+  </si>
+  <si>
+    <t>Edukacja kończy się po szkole.</t>
+  </si>
+  <si>
+    <t>To jest błędne przekonanie: nadmiernie zawęża Cel i przesłania praktyczne możliwości. Dobre pytanie quizowe często podważa błędne przekonanie, ponieważ dzięki temu wiedza lepiej zapada w pamięć.</t>
+  </si>
+  <si>
+    <t>Które zachowanie najlepiej przekłada Cel 4 z teorii na działanie?</t>
+  </si>
+  <si>
+    <t>Wybranie konkretnego usprawnienia i konsekwentne jego wdrożenie.</t>
+  </si>
+  <si>
+    <t>Robienie czegoś przeciwnego, gdy nikt nie sprawdza.</t>
+  </si>
+  <si>
+    <t>Czekanie, aż ktoś inny wszystko naprawi.</t>
+  </si>
+  <si>
+    <t>Mówienie o zrównoważonym rozwoju bez wprowadzania zmian.</t>
+  </si>
+  <si>
+    <t>Konkretne działanie sprzyja uczeniu się i przynosi mierzalną poprawę. Świadomość zrównoważonego rozwoju powinna prowadzić do praktycznej zmiany zachowania.</t>
+  </si>
+  <si>
+    <t>Co sprawia, że Cel 4 jest przydatnym tematem edukacyjnym dla pracowników?</t>
+  </si>
+  <si>
+    <t>Daje jedną idealną odpowiedź w każdej sytuacji.</t>
+  </si>
+  <si>
+    <t>Łączy globalne wyzwania z wyborami znanymi ludziom z pracy i domu.</t>
+  </si>
+  <si>
+    <t>Nie ma związku z kulturą firmy.</t>
+  </si>
+  <si>
+    <t>Eliminuje potrzebę wiedzy eksperckiej.</t>
+  </si>
+  <si>
+    <t>Najskuteczniejsze uczenie się następuje wtedy, gdy ludzie dostrzegają związek między globalnymi celami a znanymi wyborami. Cele zrównoważonego rozwoju najbardziej angażują, gdy są istotne, konkretne i powiązane z rolami ludzi.</t>
+  </si>
+  <si>
+    <t>Co przede wszystkim ma wzmacniać program YouPro?</t>
+  </si>
+  <si>
+    <t>Program wyłącznie dla zewnętrznych dostawców</t>
+  </si>
+  <si>
+    <t>Tylko krótkoterminowe promocje sprzedażowe</t>
+  </si>
+  <si>
+    <t>Rozwój osobisty i międzynarodowy networking młodych specjalistów</t>
+  </si>
+  <si>
+    <t>Zastąpienie wszystkich szkoleń technicznych</t>
+  </si>
+  <si>
+    <t>Raport opisuje YouPro jako 24-miesięczny program rozwoju osobistego i międzynarodowego networkingu. Przykłady STOCKMEIER konkretyzują Cel i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Który projekt YouPro zwiększa świadomość odpowiedzialnego korzystania z zasobów biurowych?</t>
+  </si>
+  <si>
+    <t>Trudne · Jednokrotny wybór</t>
+  </si>
+  <si>
+    <t>PaperSaver jest opisany jako projekt zwiększający świadomość odpowiedzialnego korzystania z zasobów w codziennym życiu biurowym. Przykłady STOCKMEIER konkretyzują Cel i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>W jaki sposób Zespół Ambasadorów Zrównoważonego Rozwoju wspiera uczenie się?</t>
+  </si>
+  <si>
+    <t>Poprzez wymianę pomysłów i rozwijanie wspólnych inicjatyw na rzecz zrównoważonego rozwoju</t>
+  </si>
+  <si>
+    <t>Poprzez unikanie kontaktów między krajami</t>
+  </si>
+  <si>
+    <t>Poprzez ograniczanie zrównoważonego rozwoju do jednej lokalizacji</t>
+  </si>
+  <si>
+    <t>Poprzez przejmowanie wszystkich obowiązków pracowników</t>
+  </si>
+  <si>
+    <t>Raport wyjaśnia, że ambasadorzy spotykają się, aby wymieniać pomysły i dalej rozwijać inicjatywy na rzecz zrównoważonego rozwoju. Przykłady STOCKMEIER konkretyzują Cel i pokazują, jak inicjatywy Grupy łączą się z globalnymi celami.</t>
+  </si>
+  <si>
+    <t>Które działanie w życiu prywatnym najlepiej wspiera Cel 4?</t>
+  </si>
+  <si>
+    <t>Szybkie udostępnianie dezinformacji</t>
+  </si>
+  <si>
+    <t>Uczenie się, jak codzienne wybory wpływają na zrównoważony rozwój</t>
+  </si>
+  <si>
+    <t>Zakładanie, że nauka jest tylko dla uczniów i studentów</t>
+  </si>
+  <si>
+    <t>Unikanie nowych informacji</t>
+  </si>
+  <si>
+    <t>Uczenie się pomaga ludziom podejmować lepsze decyzje także poza pracą. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera wagi, gdy są powtarzane przez wiele osób.</t>
+  </si>
+  <si>
+    <t>Jaki jest praktyczny sposób pomagania innym w nauce?</t>
+  </si>
+  <si>
+    <t>Zachowywanie przydatnej wiedzy w tajemnicy</t>
+  </si>
+  <si>
+    <t>Wyśmiewanie osób, które zadają pytania</t>
+  </si>
+  <si>
+    <t>Wyjaśnienie przydatnego nawyku związanego ze zrównoważonym rozwojem prostym językiem</t>
+  </si>
+  <si>
+    <t>Mówienie wyłącznie skomplikowanym językiem technicznym</t>
+  </si>
+  <si>
+    <t>Przystępne wyjaśnienia sprawiają, że uczenie się jest inkluzywne i użyteczne. Osobiste nawyki mają znaczenie, ponieważ wiele drobnych wyborów nabiera wagi, gdy są powtarzane przez wiele osób.</t>
+  </si>
+  <si>
+    <t>Qual è l’idea principale dell’OSS 4 – Istruzione di qualità?</t>
+  </si>
+  <si>
+    <t>Facile · Scelta singola</t>
+  </si>
+  <si>
+    <t>Si applica solo ai governi nazionali.</t>
+  </si>
+  <si>
+    <t>Si concentra sull’apprendimento permanente.</t>
+  </si>
+  <si>
+    <t>Chiede alle aziende di ignorare gli impatti a lungo termine.</t>
+  </si>
+  <si>
+    <t>È solo uno slogan di marketing senza significato pratico.</t>
+  </si>
+  <si>
+    <t>L’OSS 4 riguarda l’apprendimento permanente e la trasformazione di questo obiettivo in azioni concrete. L’OSS 4 diventa utile quando le persone traducono l’obiettivo generale in decisioni pratiche.</t>
+  </si>
+  <si>
+    <t>Perché l’OSS 4 è rilevante per un’azienda di distribuzione e produzione di prodotti chimici?</t>
+  </si>
+  <si>
+    <t>Media · Scelta singola</t>
+  </si>
+  <si>
+    <t>Perché i prodotti chimici non hanno alcun legame con la sostenibilità.</t>
+  </si>
+  <si>
+    <t>Perché la sostenibilità appartiene solo alle relazioni annuali.</t>
+  </si>
+  <si>
+    <t>Perché la formazione, la condivisione delle conoscenze e il lavoro sicuro possono influenzare le prestazioni di sostenibilità.</t>
+  </si>
+  <si>
+    <t>Perché gli OSS sostituiscono tutti i requisiti di legge.</t>
+  </si>
+  <si>
+    <t>La formazione, la condivisione delle conoscenze e il lavoro sicuro sono ambiti concreti in cui un’azienda può fare la differenza. Gli OSS collegano gli obiettivi globali alle scelte operative quotidiane.</t>
+  </si>
+  <si>
+    <t>Quale affermazione è un malinteso comune sull’OSS 4?</t>
+  </si>
+  <si>
+    <t>L’OSS 4 può essere collegato alle decisioni quotidiane.</t>
+  </si>
+  <si>
+    <t>Le aziende possono misurare e migliorare gli impatti rilevanti.</t>
+  </si>
+  <si>
+    <t>I dipendenti possono contribuire attraverso piccole abitudini.</t>
+  </si>
+  <si>
+    <t>L’istruzione termina dopo la scuola.</t>
+  </si>
+  <si>
+    <t>Questo è il malinteso: restringe troppo l’OSS e nasconde opportunità concrete. Una buona domanda di un quiz spesso mette in discussione un malinteso, perché rende l’apprendimento più memorabile.</t>
+  </si>
+  <si>
+    <t>Quale comportamento trasforma meglio l’OSS 4 dalla teoria all’azione?</t>
+  </si>
+  <si>
+    <t>Scegliere un miglioramento concreto e portarlo a termine.</t>
+  </si>
+  <si>
+    <t>Fare il contrario quando nessuno controlla.</t>
+  </si>
+  <si>
+    <t>Aspettare che qualcun altro risolva tutto.</t>
+  </si>
+  <si>
+    <t>Parlare di sostenibilità senza cambiare nulla.</t>
+  </si>
+  <si>
+    <t>L’azione concreta crea apprendimento e miglioramenti misurabili. La consapevolezza della sostenibilità dovrebbe portare a un cambiamento pratico del comportamento.</t>
+  </si>
+  <si>
+    <t>Cosa rende l’OSS 4 un utile argomento di apprendimento per i dipendenti?</t>
+  </si>
+  <si>
+    <t>Fornisce una risposta perfetta per ogni situazione.</t>
+  </si>
+  <si>
+    <t>Collega le sfide globali a scelte che le persone riconoscono sul lavoro e a casa.</t>
+  </si>
+  <si>
+    <t>Non è collegato alla cultura aziendale.</t>
+  </si>
+  <si>
+    <t>Elimina la necessità di conoscenze specialistiche.</t>
+  </si>
+  <si>
+    <t>L’apprendimento più efficace avviene quando le persone vedono il legame tra gli obiettivi globali e le scelte familiari. Gli OSS coinvolgono maggiormente quando appaiono rilevanti, concreti e collegati ai ruoli delle persone.</t>
+  </si>
+  <si>
+    <t>Che cosa mira principalmente a rafforzare il programma YouPro?</t>
+  </si>
+  <si>
+    <t>Un programma riservato ai fornitori esterni</t>
+  </si>
+  <si>
+    <t>Solo promozioni commerciali a breve termine</t>
+  </si>
+  <si>
+    <t>Lo sviluppo personale e il networking internazionale dei giovani professionisti</t>
+  </si>
+  <si>
+    <t>La sostituzione di tutta la formazione tecnica</t>
+  </si>
+  <si>
+    <t>Il rapporto descrive YouPro come un programma di 24 mesi dedicato allo sviluppo personale e al networking internazionale. Gli esempi di STOCKMEIER rendono concreto l’OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Quale progetto YouPro sensibilizza all’uso responsabile delle risorse d’ufficio?</t>
+  </si>
+  <si>
+    <t>Difficile · Scelta singola</t>
+  </si>
+  <si>
+    <t>PaperSaver è descritto come un progetto che sensibilizza all’uso responsabile delle risorse nella vita quotidiana in ufficio. Gli esempi di STOCKMEIER rendono concreto l’OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>In che modo il Sustainability Ambassador Team sostiene l’apprendimento?</t>
+  </si>
+  <si>
+    <t>Scambiando idee e sviluppando iniziative comuni di sostenibilità</t>
+  </si>
+  <si>
+    <t>Evitando i contatti tra paesi</t>
+  </si>
+  <si>
+    <t>Limitando la sostenibilità a una sola sede</t>
+  </si>
+  <si>
+    <t>Sostituendo tutte le responsabilità dei dipendenti</t>
+  </si>
+  <si>
+    <t>Il rapporto spiega che gli ambasciatori si incontrano per scambiare idee e sviluppare ulteriormente le iniziative di sostenibilità. Gli esempi di STOCKMEIER rendono concreto l’OSS e mostrano come le iniziative del Gruppo si colleghino agli obiettivi globali.</t>
+  </si>
+  <si>
+    <t>Nella vita privata, quale azione sostiene meglio l’OSS 4?</t>
+  </si>
+  <si>
+    <t>Condividere rapidamente informazioni false</t>
+  </si>
+  <si>
+    <t>Imparare come le scelte quotidiane influenzano la sostenibilità</t>
+  </si>
+  <si>
+    <t>Supporre che l’apprendimento sia solo per gli studenti</t>
+  </si>
+  <si>
+    <t>Evitare nuove informazioni</t>
+  </si>
+  <si>
+    <t>L’apprendimento aiuta le persone a prendere decisioni migliori anche al di fuori del lavoro. Le abitudini personali contano perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
+  </si>
+  <si>
+    <t>Qual è un modo pratico per aiutare gli altri a imparare?</t>
+  </si>
+  <si>
+    <t>Tenere segrete le conoscenze utili</t>
+  </si>
+  <si>
+    <t>Deridere chi fa domande</t>
+  </si>
+  <si>
+    <t>Spiegare con un linguaggio semplice un’abitudine utile per la sostenibilità</t>
+  </si>
+  <si>
+    <t>Parlare solo usando termini tecnici complicati</t>
+  </si>
+  <si>
+    <t>Spiegazioni accessibili rendono l’apprendimento inclusivo e utile. Le abitudini personali contano perché molte piccole scelte diventano significative quando vengono ripetute da molte persone.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,8 +1356,27 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -301,8 +1393,14 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -310,11 +1408,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -328,11 +1455,2007 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="90">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -343,6 +3466,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -359,6 +3486,120 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="correct"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="explanation"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Comments ZF"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{81967F02-97FF-49A7-A4FD-22D024486A47}" name="Questions_NL" displayName="Questions_NL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="76" dataDxfId="75" headerRowBorderDxfId="88" tableBorderDxfId="89" totalsRowBorderDxfId="87">
+  <autoFilter ref="A1:J11" xr:uid="{81967F02-97FF-49A7-A4FD-22D024486A47}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{F8C58993-95A9-429D-B384-C2CEC0FDFF35}" name="type" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{F83D4345-C976-4D0F-AE4C-5D263813116A}" name="question" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{F9BB3F00-E0AF-474D-BC59-DEC54F1FDA37}" name="note" dataDxfId="84"/>
+    <tableColumn id="4" xr3:uid="{9DFF9AC9-454B-445D-97D4-CE405BAD5F85}" name="option1" dataDxfId="83"/>
+    <tableColumn id="5" xr3:uid="{F30FAA0A-885A-4F20-93EC-404EA6183E69}" name="option2" dataDxfId="82"/>
+    <tableColumn id="6" xr3:uid="{3D5C557C-41C9-4B0D-B876-1C0A9ADCBD1F}" name="option3" dataDxfId="81"/>
+    <tableColumn id="7" xr3:uid="{ABFB03BC-7D2E-4C7E-825A-AEE2DD53C1AE}" name="option4" dataDxfId="80"/>
+    <tableColumn id="8" xr3:uid="{C38E2F64-6D88-4D8D-AD44-48345B5F48F7}" name="correct" dataDxfId="79"/>
+    <tableColumn id="9" xr3:uid="{9438E431-28C6-4ED3-83C1-06C0CF86E0ED}" name="explanation" dataDxfId="78"/>
+    <tableColumn id="10" xr3:uid="{C179D7A8-2326-458A-B8F5-8B9A308091E8}" name="Comments ZF" dataDxfId="77"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DCA91128-0721-41DB-8B94-4DA6FA6BC553}" name="Questions_FR" displayName="Questions_FR" ref="A1:J11" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60" headerRowBorderDxfId="73" tableBorderDxfId="74" totalsRowBorderDxfId="72">
+  <autoFilter ref="A1:J11" xr:uid="{DCA91128-0721-41DB-8B94-4DA6FA6BC553}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{BF5F6A6B-705C-4AF2-9B31-E53F7E2A26DF}" name="type" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{40755594-6DFA-4165-99BD-C5DC0418E48C}" name="question" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{158EE734-9528-4341-9F1B-DAA7FC31E9A0}" name="note" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{03292D34-D0ED-4115-A312-A0F4E4A7D860}" name="option1" dataDxfId="68"/>
+    <tableColumn id="5" xr3:uid="{E50D116A-9151-4CE0-9324-9BBF127E846F}" name="option2" dataDxfId="67"/>
+    <tableColumn id="6" xr3:uid="{F6F12269-F212-470D-9EB1-CE8BC23E0827}" name="option3" dataDxfId="66"/>
+    <tableColumn id="7" xr3:uid="{85B17DD3-821B-4832-AD71-8BC50EB5FC10}" name="option4" dataDxfId="65"/>
+    <tableColumn id="8" xr3:uid="{A8B286CF-FB5B-4249-A964-8259F75EC4CC}" name="correct" dataDxfId="64"/>
+    <tableColumn id="9" xr3:uid="{CD27B913-C743-47E9-8D66-6AC6160AC65E}" name="explanation" dataDxfId="63"/>
+    <tableColumn id="10" xr3:uid="{5907D016-FCF7-40B6-9F60-A433E5A028CB}" name="Comments ZF" dataDxfId="62"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FDF8D5D7-E35A-4AD6-A380-678FAB83BB71}" name="Questions_GE" displayName="Questions_GE" ref="A1:J11" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45" headerRowBorderDxfId="58" tableBorderDxfId="59" totalsRowBorderDxfId="57">
+  <autoFilter ref="A1:J11" xr:uid="{FDF8D5D7-E35A-4AD6-A380-678FAB83BB71}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{DC2443BA-5FBB-422D-A0F6-98645D682B5E}" name="type" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{D8643638-92F4-4D1D-8035-B608385B044A}" name="question" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{8EE1C1E3-B6FD-450C-979F-D92565C7C8D6}" name="note" dataDxfId="54"/>
+    <tableColumn id="4" xr3:uid="{574FC478-A88F-4759-A423-5077528B78DC}" name="option1" dataDxfId="53"/>
+    <tableColumn id="5" xr3:uid="{31401269-97F7-4E45-8B34-769D246978CC}" name="option2" dataDxfId="52"/>
+    <tableColumn id="6" xr3:uid="{77D1A870-51F1-48FF-93DC-B7594F7A658F}" name="option3" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{002A3B09-8F0D-4577-8FBF-E5FDCEC8E12B}" name="option4" dataDxfId="50"/>
+    <tableColumn id="8" xr3:uid="{4891F35C-F64B-40BE-B95B-AAB175A0A2C6}" name="correct" dataDxfId="49"/>
+    <tableColumn id="9" xr3:uid="{57332CB9-FAE2-4C20-A092-425E9CA8299C}" name="explanation" dataDxfId="48"/>
+    <tableColumn id="10" xr3:uid="{9EF6B262-E8FB-4E69-A907-6AFF8F6EC6AF}" name="Comments ZF" dataDxfId="47"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{14840F98-1349-4C6C-A1A7-B93283C31E22}" name="Questions_SP" displayName="Questions_SP" ref="A1:J11" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30" headerRowBorderDxfId="43" tableBorderDxfId="44" totalsRowBorderDxfId="42">
+  <autoFilter ref="A1:J11" xr:uid="{14840F98-1349-4C6C-A1A7-B93283C31E22}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{86E66597-997A-43C1-BB00-7B3D9E811437}" name="type" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{8412363E-4EC3-4C4B-AC64-9CD5EC5D40DC}" name="question" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{06D4E4D2-C9E9-4535-98BD-5051C88E2678}" name="note" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{2921AB2F-EABF-4534-9988-D918A8303D31}" name="option1" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{49312F19-CC1B-45FF-BE71-246126F98F1E}" name="option2" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{3A499FAB-23C3-459C-8540-618CE8579638}" name="option3" dataDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{75F6B6DF-C9BC-4492-A8F8-5FE9977402AF}" name="option4" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{4C94DBAD-3C27-495A-97F8-9D5B03743AF0}" name="correct" dataDxfId="34"/>
+    <tableColumn id="9" xr3:uid="{9F122B33-8B7C-4FC3-B443-F3272B0BEEB3}" name="explanation" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{4E88DC53-2534-4CF6-9252-7BFE3CE171B4}" name="Comments ZF" dataDxfId="32"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{41BA60AC-7E1F-403C-940B-54964BE56450}" name="Questions_IT" displayName="Questions_IT" ref="A1:J11" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:J11" xr:uid="{41BA60AC-7E1F-403C-940B-54964BE56450}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{4D252DF2-294A-4FED-806A-794F410C5189}" name="type" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{0746B6FB-D630-4CB7-97B6-E034AF05FA42}" name="question" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{3FE969FE-4E3B-4EA6-92A9-7178A99F5AD3}" name="note" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{8A227F23-8484-4A94-889F-2F5D3CA6FAD1}" name="option1" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{313BD530-C6BE-417B-BAC1-FBAC5BA4AB3F}" name="option2" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{CC5DD32D-DDC9-40FB-A04E-E36391D9A25F}" name="option3" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{284BADE6-69A7-4AEE-8BD2-DD8C16DE1F30}" name="option4" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{DB082A70-0C56-46A2-AA0F-CD2BC10CC3D8}" name="correct" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{A71301DB-69E2-43A8-8617-877A30F12047}" name="explanation" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{D5EFC3CB-3247-4547-9691-A90825F4CE8D}" name="Comments ZF" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{96DF7B58-AA4C-4F42-B816-0D81A888E6E1}" name="Questions_PL" displayName="Questions_PL" ref="A1:J11" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" headerRowBorderDxfId="28" tableBorderDxfId="29" totalsRowBorderDxfId="27">
+  <autoFilter ref="A1:J11" xr:uid="{96DF7B58-AA4C-4F42-B816-0D81A888E6E1}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{01063A59-88C4-4B50-826F-08ECBAB10DA0}" name="type" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{7864FF4C-5D6B-45BA-BEB4-9990926A41F4}" name="question" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{A58B761C-14DD-4C0B-A9E5-AEF2DADFF398}" name="note" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{AAFC8616-9027-4E23-AD66-62B8E176413C}" name="option1" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{AD75C876-C853-4AE2-8248-A79B9FB2868F}" name="option2" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{83BFB0D0-DE80-4721-85E7-3C3D9FCD7B0C}" name="option3" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{6CADD798-AEF7-41B4-8DFF-A27EEE631987}" name="option4" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{FF92C3C6-EFE5-40F1-9F2B-314EA2CDF604}" name="correct" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{D0713801-D713-4D0B-B8DA-AEDEE0AA9449}" name="explanation" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{7D41558A-9B9D-4C31-B9F6-9F42B48997FE}" name="Comments ZF" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -650,7 +3891,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
@@ -661,7 +3902,7 @@
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1">
+    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +3934,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="72" customHeight="1">
+    <row r="2" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -723,7 +3964,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" ht="72" customHeight="1">
+    <row r="3" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -753,7 +3994,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10" ht="72" customHeight="1">
+    <row r="4" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -783,7 +4024,7 @@
       </c>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="72" customHeight="1">
+    <row r="5" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -813,7 +4054,7 @@
       </c>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="72" customHeight="1">
+    <row r="6" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -843,7 +4084,7 @@
       </c>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="72" customHeight="1">
+    <row r="7" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -873,7 +4114,7 @@
       </c>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="72" customHeight="1">
+    <row r="8" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -903,7 +4144,7 @@
       </c>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="72" customHeight="1">
+    <row r="9" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -933,7 +4174,7 @@
       </c>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="72" customHeight="1">
+    <row r="10" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -963,7 +4204,7 @@
       </c>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="72" customHeight="1">
+    <row r="11" spans="1:10" ht="72" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -995,6 +4236,2130 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9762C6B-55B2-4E63-96F6-58795D8755F4}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="4" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="8">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="8">
+        <v>3</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="5">
+        <v>4</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" s="5">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="H11" s="10">
+        <v>3</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88895409-B04A-4CC6-8F51-EB07044B3AB6}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="4" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" s="8">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="H7" s="8">
+        <v>3</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="5">
+        <v>4</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H10" s="5">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="H11" s="10">
+        <v>3</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9609C5AB-ECEA-4B7C-A9F7-5A81C4EFB8DE}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="4" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="H3" s="8">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="H7" s="8">
+        <v>3</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="5">
+        <v>4</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="H10" s="5">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="H11" s="10">
+        <v>3</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39524BC5-A17C-4034-B32C-96D8CC613D25}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="4" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H3" s="8">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="H7" s="8">
+        <v>3</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="5">
+        <v>4</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="H10" s="5">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="H11" s="10">
+        <v>3</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04CECE00-6964-4260-8AA9-734A4D42E78F}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="4" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="H3" s="8">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="H7" s="8">
+        <v>3</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="5">
+        <v>4</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="H10" s="5">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="H11" s="10">
+        <v>3</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB49C994-5CAA-4415-83F1-85484F4A2F40}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.26953125" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="4" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="18.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="H3" s="8">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="J4" s="5"/>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="H6" s="5">
+        <v>2</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="H7" s="8">
+        <v>3</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="J7" s="8"/>
+    </row>
+    <row r="8" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="5">
+        <v>4</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="H9" s="8">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="H10" s="5">
+        <v>2</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="H11" s="10">
+        <v>3</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="J11" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1185,13 +6550,37 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D07FCDD9-54C6-4B60-BD57-38540436E191}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D07FCDD9-54C6-4B60-BD57-38540436E191}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9900B929-460C-49B5-A602-75235A2C1A4B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9900B929-460C-49B5-A602-75235A2C1A4B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2D71649-6956-45BF-ACA9-1483A9203C62}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2D71649-6956-45BF-ACA9-1483A9203C62}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2aad7df3-4ab7-4daa-980d-cf7206357ce9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>